--- a/lft/eu2027/out/EU-hand-baggage-2027-by-airline.xlsx
+++ b/lft/eu2027/out/EU-hand-baggage-2027-by-airline.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -545,66 +545,66 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>THE RULE, AS USED IN THIS ANALYSIS</t>
+          <t>THE ACT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Free personal item: 40 x 30 x 15 cm, under the seat</t>
+          <t>Regulation (EU) 2026/2202 of 16 September 2026 — amending Regulation (EC) 261/2004</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Parliament 2026-07-07 · Council 2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>THE RULE, AS USED IN THIS ANALYSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Free personal item: 40 x 30 x 15 cm, under the seat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Free cabin bag: 100 cm total of the three dimensions, 7 kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Fares must be shown inclusive of hand baggage at the start of booking</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Parliament 2026-07-07 · Council 2026-07-13 · application expected 2027-10-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>VERIFICATION STATUS — READ BEFORE PUBLISHING</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>The allowance data is taken from each airline's published terms and is the basis of a live</t>
+          <t>Fares must be shown inclusive of hand baggage at the start of booking</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>public tool. The REGULATION figures above are from reporting on the adopted text and have NOT</t>
+          <t>Applies from 2027-10-23 (= OJ publication + 20 days + 12 months)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>been read against the Official Journal. Verify them at source before printing.</t>
+          <t>Airlines may still sell a cheaper fare to a passenger who waives the cabin bag.</t>
         </is>
       </c>
     </row>
@@ -614,105 +614,195 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SCOPE — the honest caveat</t>
+          <t>VERIFICATION STATUS — READ BEFORE PUBLISHING</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>EU/EEA carriers are treated as in scope. Non-EU carriers are marked as in scope on EU</t>
+          <t>The allowance data is taken from each airline's published terms and is the basis of a live</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>departures only. That is a plain reading, not a legal opinion, and a lawyer should confirm it</t>
+          <t>public tool. The REGULATION figures are graded, because the primary text could not be read:</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>before it is asserted as fact.</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED by several independent sources:</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>WHAT IS NOT IN HERE</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the regulation number and date; Parliament 7 Jul and Council 13 Jul 2026; the free personal</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Prices. The add-on price columns are deliberately empty. No verified price data was available</t>
+          <t xml:space="preserve">  item at 40 x 30 x 15 cm; application = OJ publication + 20 days + 12 months; and the</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>and nothing has been estimated. Those columns are for filling, not for citing as they stand.</t>
+          <t xml:space="preserve">  requirement to display fares inclusive of hand baggage.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>CORROBORATED, but one outlet dissents:</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>THE SHEETS</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the 100 cm / 7 kg cabin bag included in the standard fare, and the 23 Oct 2027 date.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Summary by airline — one row per carrier, the at-a-glance view</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED:</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Every fare — all 112 products with the full working</t>
+          <t xml:space="preserve">  the Official Journal publication date, and any article text. Nothing here has been read</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  against the regulation itself. Do that before printing any of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SCOPE — the honest caveat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>EU/EEA carriers are treated as in scope. Non-EU carriers are marked as in scope on EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>departures only. That is a plain reading, not a legal opinion, and a lawyer should confirm it</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>before it is asserted as fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>WHAT IS NOT IN HERE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Prices. The add-on price columns are deliberately empty. No verified price data was available</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>and nothing has been estimated. Those columns are for filling, not for citing as they stand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>THE SHEETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Summary by airline — one row per carrier, the at-a-glance view</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Every fare — all 112 products with the full working</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>Paid becomes free — add-ons the entitlement abolishes outright</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Paid products that shrink — add-ons surviving only for oversized bags</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Below the floor — free allowances smaller than 40 x 30 x 15</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Contact: glen@luggagefortravel.com</t>
         </is>
@@ -3256,7 +3346,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr"/>
@@ -3467,7 +3557,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
@@ -3678,7 +3768,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr"/>
@@ -6462,7 +6552,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr"/>
@@ -7493,7 +7583,7 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr"/>
@@ -7702,7 +7792,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr"/>
@@ -7909,7 +7999,7 @@
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr"/>
@@ -11044,7 +11134,7 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr"/>
@@ -11111,7 +11201,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr"/>
@@ -11178,7 +11268,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr"/>
@@ -11245,7 +11335,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
@@ -11310,7 +11400,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
@@ -11377,7 +11467,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr"/>
@@ -11442,7 +11532,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Survives only for bags above the free entitlement</t>
+          <t>Inverts — bag becomes the default fare, no-bag becomes the discount</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr"/>
